--- a/sample-data/sample-run/selections/Chain Ladder Selections - Tail.xlsx
+++ b/sample-data/sample-run/selections/Chain Ladder Selections - Tail.xlsx
@@ -2492,7 +2492,7 @@
         <v>0.01308143486613297</v>
       </c>
       <c r="D36" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
@@ -2501,26 +2501,30 @@
       </c>
       <c r="F36" s="15" t="inlineStr"/>
       <c r="G36" s="16" t="n">
-        <v>1</v>
+        <v>1.0119</v>
       </c>
       <c r="H36" s="16" t="n"/>
-      <c r="I36" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="I36" s="16" t="n"/>
       <c r="J36" s="16" t="n"/>
       <c r="K36" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L36" s="18" t="n"/>
+      <c r="L36" s="18" t="n">
+        <v>0.442356217608501</v>
+      </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N36" s="19" t="n"/>
-      <c r="O36" s="19" t="n"/>
+      <c r="N36" s="19" t="n">
+        <v>1074519.444381315</v>
+      </c>
+      <c r="O36" s="19" t="n">
+        <v>1969952.314699076</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="20" t="n">
@@ -2535,7 +2539,7 @@
         <v>0.01308143486613297</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
@@ -2544,20 +2548,20 @@
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
-          <t>[-6.451672874219806, 0.35039433553951527, -0.016429559529301863]</t>
+          <t>[-6.443260556945541, 0.34069008345644103, -0.01501500915121795]</t>
         </is>
       </c>
       <c r="G37" s="22" t="n">
-        <v>1.072330676248243</v>
+        <v>1.077782958006554</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>0.2881506281144713</v>
+        <v>0.3319356148418592</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>0.009975792381201965</v>
+        <v>0.01009648961399146</v>
       </c>
       <c r="J37" s="22" t="n">
-        <v>0.0006221196357342844</v>
+        <v>0.0006087900176089292</v>
       </c>
       <c r="K37" s="21" t="inlineStr">
         <is>
@@ -2565,7 +2569,7 @@
         </is>
       </c>
       <c r="L37" s="24" t="n">
-        <v>2.270884035914176</v>
+        <v>2.65434800617516</v>
       </c>
       <c r="M37" s="21" t="inlineStr">
         <is>
@@ -2573,10 +2577,10 @@
         </is>
       </c>
       <c r="N37" s="25" t="n">
-        <v>947431.4984121136</v>
+        <v>1008835.979166448</v>
       </c>
       <c r="O37" s="25" t="n">
-        <v>1736957.747088876</v>
+        <v>1849532.628471822</v>
       </c>
     </row>
     <row r="38">
@@ -2592,7 +2596,7 @@
         <v>0.01308143486613297</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
@@ -2605,7 +2609,7 @@
         </is>
       </c>
       <c r="G38" s="22" t="n">
-        <v>1.000000000000035</v>
+        <v>1.000000000000008</v>
       </c>
       <c r="H38" s="22" t="n"/>
       <c r="I38" s="22" t="n"/>
@@ -2616,7 +2620,7 @@
         </is>
       </c>
       <c r="L38" s="24" t="n">
-        <v>1.20857749788252e-12</v>
+        <v>3.187953535252938e-13</v>
       </c>
       <c r="M38" s="21" t="inlineStr">
         <is>
@@ -2624,10 +2628,10 @@
         </is>
       </c>
       <c r="N38" s="25" t="n">
-        <v>1015959.859391116</v>
+        <v>1087306.225769445</v>
       </c>
       <c r="O38" s="25" t="n">
-        <v>1862593.075550377</v>
+        <v>1993394.747243982</v>
       </c>
     </row>
     <row r="39">
@@ -2643,7 +2647,7 @@
         <v>0.01308143486613297</v>
       </c>
       <c r="D39" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
@@ -2652,7 +2656,7 @@
       </c>
       <c r="F39" s="15" t="inlineStr"/>
       <c r="G39" s="16" t="n">
-        <v>1</v>
+        <v>1.0238</v>
       </c>
       <c r="H39" s="16" t="n"/>
       <c r="I39" s="16" t="n"/>
@@ -2662,14 +2666,20 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L39" s="18" t="n"/>
+      <c r="L39" s="18" t="n">
+        <v>0.8706671837994439</v>
+      </c>
       <c r="M39" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N39" s="19" t="n"/>
-      <c r="O39" s="19" t="n"/>
+      <c r="N39" s="19" t="n">
+        <v>1062029.913820524</v>
+      </c>
+      <c r="O39" s="19" t="n">
+        <v>1947054.842004288</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="n">
@@ -2684,7 +2694,7 @@
         <v>0.01308143486613297</v>
       </c>
       <c r="D40" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
@@ -2693,7 +2703,7 @@
       </c>
       <c r="F40" s="15" t="inlineStr"/>
       <c r="G40" s="16" t="n">
-        <v>1</v>
+        <v>1.02394161</v>
       </c>
       <c r="H40" s="16" t="n"/>
       <c r="I40" s="16" t="n"/>
@@ -2703,14 +2713,20 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L40" s="18" t="n"/>
+      <c r="L40" s="18" t="n">
+        <v>0.8756822210251475</v>
+      </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N40" s="19" t="n"/>
-      <c r="O40" s="19" t="n"/>
+      <c r="N40" s="19" t="n">
+        <v>1061883.036249939</v>
+      </c>
+      <c r="O40" s="19" t="n">
+        <v>1946785.566458225</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="n">
@@ -2725,7 +2741,7 @@
         <v>0.01123156187314335</v>
       </c>
       <c r="D41" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
@@ -2734,26 +2750,30 @@
       </c>
       <c r="F41" s="15" t="inlineStr"/>
       <c r="G41" s="16" t="n">
-        <v>1</v>
+        <v>1.0119</v>
       </c>
       <c r="H41" s="16" t="n"/>
-      <c r="I41" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="I41" s="16" t="n"/>
       <c r="J41" s="16" t="n"/>
       <c r="K41" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L41" s="18" t="n"/>
+      <c r="L41" s="18" t="n">
+        <v>0.442356217608501</v>
+      </c>
       <c r="M41" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N41" s="19" t="n"/>
-      <c r="O41" s="19" t="n"/>
+      <c r="N41" s="19" t="n">
+        <v>1074519.444381315</v>
+      </c>
+      <c r="O41" s="19" t="n">
+        <v>1969952.314699076</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="20" t="n">
@@ -2768,7 +2788,7 @@
         <v>0.01123156187314335</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
@@ -2777,20 +2797,20 @@
       </c>
       <c r="F42" s="21" t="inlineStr">
         <is>
-          <t>[-6.188025216308844, 0.7237043892586503, -0.058938903899493855]</t>
+          <t>[-6.198815549455116, 0.8016226533428397, -0.08285309337556246]</t>
         </is>
       </c>
       <c r="G42" s="22" t="n">
-        <v>1.081214121009459</v>
+        <v>1.021551350628563</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>0.8843474001970071</v>
+        <v>0.8862026012818859</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>0.01563919154248875</v>
+        <v>0.003719995419637236</v>
       </c>
       <c r="J42" s="22" t="n">
-        <v>5.387871727770147e-05</v>
+        <v>3.183582064846544e-05</v>
       </c>
       <c r="K42" s="21" t="inlineStr">
         <is>
@@ -2798,7 +2818,7 @@
         </is>
       </c>
       <c r="L42" s="24" t="n">
-        <v>2.522331501092271</v>
+        <v>0.7907778494008147</v>
       </c>
       <c r="M42" s="21" t="inlineStr">
         <is>
@@ -2806,10 +2826,10 @@
         </is>
       </c>
       <c r="N42" s="25" t="n">
-        <v>939647.2351310179</v>
+        <v>1064367.665022835</v>
       </c>
       <c r="O42" s="25" t="n">
-        <v>1722686.597740196</v>
+        <v>1951340.719208539</v>
       </c>
     </row>
     <row r="43">
@@ -2825,7 +2845,7 @@
         <v>0.01123156187314335</v>
       </c>
       <c r="D43" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43" s="21" t="inlineStr">
         <is>
@@ -2838,7 +2858,7 @@
         </is>
       </c>
       <c r="G43" s="22" t="n">
-        <v>1.000000000000146</v>
+        <v>1.000000000000038</v>
       </c>
       <c r="H43" s="22" t="n"/>
       <c r="I43" s="22" t="n"/>
@@ -2849,7 +2869,7 @@
         </is>
       </c>
       <c r="L43" s="24" t="n">
-        <v>5.025540608282893e-12</v>
+        <v>1.434579090863764e-12</v>
       </c>
       <c r="M43" s="21" t="inlineStr">
         <is>
@@ -2857,10 +2877,10 @@
         </is>
       </c>
       <c r="N43" s="25" t="n">
-        <v>1015959.859391008</v>
+        <v>1087306.225769412</v>
       </c>
       <c r="O43" s="25" t="n">
-        <v>1862593.075550172</v>
+        <v>1993394.747243918</v>
       </c>
     </row>
     <row r="44">
@@ -2876,7 +2896,7 @@
         <v>0.01123156187314335</v>
       </c>
       <c r="D44" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
@@ -2885,7 +2905,7 @@
       </c>
       <c r="F44" s="15" t="inlineStr"/>
       <c r="G44" s="16" t="n">
-        <v>1</v>
+        <v>1.0238</v>
       </c>
       <c r="H44" s="16" t="n"/>
       <c r="I44" s="16" t="n"/>
@@ -2895,14 +2915,20 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L44" s="18" t="n"/>
+      <c r="L44" s="18" t="n">
+        <v>0.8706671837994439</v>
+      </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N44" s="19" t="n"/>
-      <c r="O44" s="19" t="n"/>
+      <c r="N44" s="19" t="n">
+        <v>1062029.913820524</v>
+      </c>
+      <c r="O44" s="19" t="n">
+        <v>1947054.842004288</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="n">
@@ -2917,7 +2943,7 @@
         <v>0.01123156187314335</v>
       </c>
       <c r="D45" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
@@ -2926,7 +2952,7 @@
       </c>
       <c r="F45" s="15" t="inlineStr"/>
       <c r="G45" s="16" t="n">
-        <v>1</v>
+        <v>1.02394161</v>
       </c>
       <c r="H45" s="16" t="n"/>
       <c r="I45" s="16" t="n"/>
@@ -2936,14 +2962,20 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L45" s="18" t="n"/>
+      <c r="L45" s="18" t="n">
+        <v>0.8756822210251475</v>
+      </c>
       <c r="M45" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N45" s="19" t="n"/>
-      <c r="O45" s="19" t="n"/>
+      <c r="N45" s="19" t="n">
+        <v>1061883.036249939</v>
+      </c>
+      <c r="O45" s="19" t="n">
+        <v>1946785.566458225</v>
+      </c>
     </row>
     <row r="46"/>
     <row r="47">
@@ -3000,16 +3032,16 @@
         <v>203</v>
       </c>
       <c r="C49" s="33" t="n">
-        <v>1</v>
+        <v>1.0216</v>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>mcclenahan</t>
+          <t>double_exp</t>
         </is>
       </c>
       <c r="E49" s="34" t="inlineStr">
         <is>
-          <t>Incurred loss triangle — expect medium tail length, materially shorter than paid loss. Selected starting age 203: monotonicity fails at both available starting ages (203 has 4 slope_sign_changes vs 143's 8, indicating more stability at later age), but materiality anchor applies strongly here. McClenahan method produces tail = 1.0000 with materiality_ok=True, confirming tail is immaterial (&lt;0.1% of CDF, pct_of_cdf = 1.2e-12%). Gap_flag=False confirms smooth transition. Observed factors at late ages (143–203 months) consistently cluster at 1.000–1.001, supporting minimal tail. Alternative age 203 double_exp (R²=0.884, tail=1.0812) produces material tail (2.52% of CDF) without compelling justification. Age 143 rejected due to higher slope_sign_changes (8 vs 4) and poor double_exp fit (R²=0.288). Framework Point 1 (Triangle Type): Incurred loss — expect shorter tail than paid. Point 2 (Starting Age): Monotonicity violated at both ages; selected 203 due to fewer slope breaks. Point 3 (Curve Form): mcclenahan for synthetic incremental fit. Point 4 (Fitting Method): N/A for mcclenahan. Point 5 (Weights): N/A. Point 6 (Diagnostics): No R² available for mcclenahan; immaterial tail validates selection. Point 7 (Gap Rule): gap_flag=False. Point 8 (Blending): Not applicable. Point 9 (Benchmarks): Incurred loss tails typically 1.010–1.030; tail=1.0000 is conservative but justified by immateriality. Point 10 (Overrides): None. Point 11 (Anchor Rule): Materiality anchor applies (tail &lt;0.1% of CDF). Point 12 (Sensitivity): Reserve sensitivity immaterial (pct_of_cdf ~ 0). Point 13 (Prior Consistency): No prior provided; documenting baseline. Point 14 (Environmental): No environmental changes noted; pattern stable across study period. Point 15 (Documentation): All fields completed; rationale fully traceable.</t>
+          <t>Incurred loss triangle — expect medium-length tail, shorter than Paid Loss but longer than Reported Count. Selected starting age 203 (16.75 years): is_monotone_from_here=False but cv=0.011 (low), slope_sign_changes=5. Although observed factors show late-age volatility (not monotone), double exponential curve method effectively captures non-monotone decay patterns through log-quadratic fitting. Gap_flag=False with gap_to_last_observed=0.00003 confirms excellent smooth transition from observed factors to fitted curve — curve rejoins observed LDFs at switchover age. WLS fit on log(factor−1) from age 203 onward using 7 selected LDF intervals. Double exponential selected over simpler methods (bondy, modified bondy) because excellent R²=0.886 and stable LOO std dev=0.0037 justify more sophisticated curve form. Age 203 preferred over earlier age 143 due to structural stability: slope_sign_changes=5 vs 9 at age 143. Closure anchor applies: at 203 months (16.75 years), casualty line expected &gt;95% closed, losses substantively complete. Tail 0.79% of CDF is material but defensible — materiality anchor does not apply (&gt;0.1% threshold). Paid loss tail materially longer than incurred (1.045 vs 1.0216) as expected for casualty line.</t>
         </is>
       </c>
       <c r="F49" s="34" t="inlineStr"/>
@@ -3024,7 +3056,7 @@
         <v>203</v>
       </c>
       <c r="C50" s="36" t="n">
-        <v>1.0812</v>
+        <v>1.021551350628563</v>
       </c>
       <c r="D50" s="37" t="inlineStr">
         <is>
@@ -3033,7 +3065,7 @@
       </c>
       <c r="E50" s="37" t="inlineStr">
         <is>
-          <t>Age 203 Double Exponential selected based on superior diagnostic strength (R² = 0.884 vs 0.288 at age 143) and smooth connection to observed data (gap = 0.000054). Observed tail factors are flat near 1.0 from age 143 onward; Double Exponential at age 203 captures this stability while extrapolating a modest, reasonable tail. McClenahan at both ages returns 1.0 with materiality_ok = True, but the Double Exponential curve structure (based on 8 mature AYs at age 203 vs 13 at 143) provides stronger statistical support. The 1.0812 tail is conservative relative to industry norms and the curve form. Prior comparisons and sensitivity show this is within reasonable bounds.</t>
+          <t>Selected double exponential at age 203 based on strongest diagnostic evidence. At age 203, the triangle shows mature, stable development with only 8 accident years contributing and tightly clustered observed factors around 1.02. The double exponential model demonstrates superior fit quality with R²=0.8862 and very tight LOO stability (std dev=0.0037), indicating smooth connection to observed data. The gap to the last observed factor (0.000032) is negligible. Starting at age 203 rather than 143 is more defensible because it focuses on the most mature tail development with lower CV (0.0112 vs 0.0131) and fewer slope sign changes (5 vs 9). The tail factor of 1.02155 reflects a realistic tail development pattern for stable, mature incurred loss data.</t>
         </is>
       </c>
       <c r="F50" s="37" t="inlineStr"/>
@@ -4938,7 +4970,7 @@
         </is>
       </c>
       <c r="L36" s="18" t="n">
-        <v>0.06164545593810963</v>
+        <v>0.06438163580663937</v>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
@@ -4946,10 +4978,10 @@
         </is>
       </c>
       <c r="N36" s="19" t="n">
-        <v>518266.2217693701</v>
+        <v>538010.4569293708</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>950154.7399105057</v>
+        <v>986352.5043705106</v>
       </c>
     </row>
     <row r="37">
@@ -4974,20 +5006,20 @@
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
-          <t>[0.011941365596704483, 0.8717942642959445]</t>
+          <t>[0.011177496545769987, 0.8778658345737793]</t>
         </is>
       </c>
       <c r="G37" s="22" t="n">
-        <v>1.018095619722987</v>
+        <v>1.01933590852198</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>0.2308473328047094</v>
+        <v>0.2043244170662153</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>0.002004170803278808</v>
+        <v>0.002142901295164464</v>
       </c>
       <c r="J37" s="22" t="n">
-        <v>0.008158634403295523</v>
+        <v>0.006322503454230084</v>
       </c>
       <c r="K37" s="21" t="inlineStr">
         <is>
@@ -4995,7 +5027,7 @@
         </is>
       </c>
       <c r="L37" s="24" t="n">
-        <v>0.2814204784861253</v>
+        <v>0.3135817658082761</v>
       </c>
       <c r="M37" s="21" t="inlineStr">
         <is>
@@ -5003,10 +5035,10 @@
         </is>
       </c>
       <c r="N37" s="25" t="n">
-        <v>511039.8767611086</v>
+        <v>529863.3092348725</v>
       </c>
       <c r="O37" s="25" t="n">
-        <v>936906.4407287091</v>
+        <v>971416.066930607</v>
       </c>
     </row>
     <row r="38">
@@ -5031,20 +5063,20 @@
       </c>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t>[0.011941365596704483, 0.8717942642959445]</t>
+          <t>[0.011177496545769987, 0.8778658345737793]</t>
         </is>
       </c>
       <c r="G38" s="22" t="n">
-        <v>1.031078396186502</v>
+        <v>1.032279927640226</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>0.2308473328047094</v>
+        <v>0.2043244170662153</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>0.002004170803278808</v>
+        <v>0.002142901295164464</v>
       </c>
       <c r="J38" s="22" t="n">
-        <v>0.008158634403295523</v>
+        <v>0.006322503454230084</v>
       </c>
       <c r="K38" s="21" t="inlineStr">
         <is>
@@ -5052,7 +5084,7 @@
         </is>
       </c>
       <c r="L38" s="24" t="n">
-        <v>0.4763082572070689</v>
+        <v>0.5158890893731068</v>
       </c>
       <c r="M38" s="21" t="inlineStr">
         <is>
@@ -5060,10 +5092,10 @@
         </is>
       </c>
       <c r="N38" s="25" t="n">
-        <v>504605.1415281072</v>
+        <v>523219.2191764042</v>
       </c>
       <c r="O38" s="25" t="n">
-        <v>925109.4261348695</v>
+        <v>959235.2351567447</v>
       </c>
     </row>
     <row r="39">
@@ -5088,20 +5120,20 @@
       </c>
       <c r="F39" s="21" t="inlineStr">
         <is>
-          <t>[0.011941365596704483, 0.8717942642959445]</t>
+          <t>[0.011177496545769987, 0.8778658345737793]</t>
         </is>
       </c>
       <c r="G39" s="22" t="n">
-        <v>1.045910828459935</v>
+        <v>1.047200108442484</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>0.2308473328047094</v>
+        <v>0.2043244170662153</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>0.002004170803278808</v>
+        <v>0.002142901295164464</v>
       </c>
       <c r="J39" s="22" t="n">
-        <v>0.008158634403295523</v>
+        <v>0.006322503454230084</v>
       </c>
       <c r="K39" s="21" t="inlineStr">
         <is>
@@ -5109,7 +5141,7 @@
         </is>
       </c>
       <c r="L39" s="24" t="n">
-        <v>0.6921477023809712</v>
+        <v>0.7419024665727737</v>
       </c>
       <c r="M39" s="21" t="inlineStr">
         <is>
@@ -5117,10 +5149,10 @@
         </is>
       </c>
       <c r="N39" s="25" t="n">
-        <v>497449.1571144387</v>
+        <v>515764.5547943115</v>
       </c>
       <c r="O39" s="25" t="n">
-        <v>911990.1213764772</v>
+        <v>945568.3504562378</v>
       </c>
     </row>
     <row r="40">
@@ -5145,11 +5177,11 @@
       </c>
       <c r="F40" s="21" t="inlineStr">
         <is>
-          <t>{"r": 0.40152706}</t>
+          <t>{"r": 0.41441939}</t>
         </is>
       </c>
       <c r="G40" s="22" t="n">
-        <v>1.000000000765223</v>
+        <v>1.000000001581377</v>
       </c>
       <c r="H40" s="22" t="n"/>
       <c r="I40" s="22" t="n"/>
@@ -5160,7 +5192,7 @@
         </is>
       </c>
       <c r="L40" s="24" t="n">
-        <v>1.215017709210326e-08</v>
+        <v>2.62242475825969e-08</v>
       </c>
       <c r="M40" s="21" t="inlineStr">
         <is>
@@ -5168,10 +5200,10 @@
         </is>
       </c>
       <c r="N40" s="25" t="n">
-        <v>520287.4596361294</v>
+        <v>540108.696857281</v>
       </c>
       <c r="O40" s="25" t="n">
-        <v>953860.3426662385</v>
+        <v>990199.2775716782</v>
       </c>
     </row>
     <row r="41">
@@ -5207,7 +5239,7 @@
         </is>
       </c>
       <c r="L41" s="18" t="n">
-        <v>0.1227387215598515</v>
+        <v>0.1281830938677425</v>
       </c>
       <c r="M41" s="15" t="inlineStr">
         <is>
@@ -5215,10 +5247,10 @@
         </is>
       </c>
       <c r="N41" s="19" t="n">
-        <v>516260.627142556</v>
+        <v>535928.4557564855</v>
       </c>
       <c r="O41" s="19" t="n">
-        <v>946477.8164280131</v>
+        <v>982535.5022202358</v>
       </c>
     </row>
     <row r="42">
@@ -5254,7 +5286,7 @@
         </is>
       </c>
       <c r="L42" s="18" t="n">
-        <v>0.1229759140267765</v>
+        <v>0.1284307940500395</v>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
@@ -5262,10 +5294,10 @@
         </is>
       </c>
       <c r="N42" s="19" t="n">
-        <v>516252.8357101008</v>
+        <v>535920.3674961403</v>
       </c>
       <c r="O42" s="19" t="n">
-        <v>946463.5321351737</v>
+        <v>982520.6737429202</v>
       </c>
     </row>
     <row r="43">
@@ -5301,7 +5333,7 @@
         </is>
       </c>
       <c r="L43" s="18" t="n">
-        <v>0.06164545593810963</v>
+        <v>0.06438163580663937</v>
       </c>
       <c r="M43" s="15" t="inlineStr">
         <is>
@@ -5309,10 +5341,10 @@
         </is>
       </c>
       <c r="N43" s="19" t="n">
-        <v>518266.2217693701</v>
+        <v>538010.4569293708</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>950154.7399105057</v>
+        <v>986352.5043705106</v>
       </c>
     </row>
     <row r="44">
@@ -5337,18 +5369,18 @@
       </c>
       <c r="F44" s="21" t="inlineStr">
         <is>
-          <t>[-6.0197845785918815, 0.24717142993689123, -0.016926013800853207]</t>
+          <t>[-6.096959287614572, 0.299484379146448, -0.024191440033221767]</t>
         </is>
       </c>
       <c r="G44" s="22" t="n">
-        <v>1.045603069011225</v>
+        <v>1.030622076984349</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>0.4657683173472149</v>
+        <v>0.5149627228015914</v>
       </c>
       <c r="I44" s="22" t="n"/>
       <c r="J44" s="22" t="n">
-        <v>0.0001301930542501879</v>
+        <v>0.0001496980143577326</v>
       </c>
       <c r="K44" s="21" t="inlineStr">
         <is>
@@ -5356,7 +5388,7 @@
         </is>
       </c>
       <c r="L44" s="24" t="n">
-        <v>0.6877408240592454</v>
+        <v>0.4903070513075852</v>
       </c>
       <c r="M44" s="21" t="inlineStr">
         <is>
@@ -5364,10 +5396,10 @@
         </is>
       </c>
       <c r="N44" s="25" t="n">
-        <v>497595.5747014806</v>
+        <v>524060.8655422702</v>
       </c>
       <c r="O44" s="25" t="n">
-        <v>912258.5536193699</v>
+        <v>960778.2534941733</v>
       </c>
     </row>
     <row r="45">
@@ -5407,7 +5439,7 @@
         </is>
       </c>
       <c r="L45" s="24" t="n">
-        <v>1.045358375314495e-05</v>
+        <v>1.091787278674837e-05</v>
       </c>
       <c r="M45" s="21" t="inlineStr">
         <is>
@@ -5415,10 +5447,10 @@
         </is>
       </c>
       <c r="N45" s="25" t="n">
-        <v>520287.1174922213</v>
+        <v>540108.3421196267</v>
       </c>
       <c r="O45" s="25" t="n">
-        <v>953859.7154024094</v>
+        <v>990198.6272193119</v>
       </c>
     </row>
     <row r="46">
@@ -5454,7 +5486,7 @@
         </is>
       </c>
       <c r="L46" s="18" t="n">
-        <v>0.1227387215598515</v>
+        <v>0.1281830938677425</v>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
@@ -5462,10 +5494,10 @@
         </is>
       </c>
       <c r="N46" s="19" t="n">
-        <v>516260.627142556</v>
+        <v>535928.4557564855</v>
       </c>
       <c r="O46" s="19" t="n">
-        <v>946477.8164280131</v>
+        <v>982535.5022202358</v>
       </c>
     </row>
     <row r="47">
@@ -5501,7 +5533,7 @@
         </is>
       </c>
       <c r="L47" s="18" t="n">
-        <v>0.1229759140267765</v>
+        <v>0.1284307940500395</v>
       </c>
       <c r="M47" s="15" t="inlineStr">
         <is>
@@ -5509,10 +5541,10 @@
         </is>
       </c>
       <c r="N47" s="19" t="n">
-        <v>516252.8357101008</v>
+        <v>535920.3674961403</v>
       </c>
       <c r="O47" s="19" t="n">
-        <v>946463.5321351737</v>
+        <v>982520.6737429202</v>
       </c>
     </row>
     <row r="48">
@@ -5554,7 +5586,7 @@
         </is>
       </c>
       <c r="L48" s="24" t="n">
-        <v>3.783066096461237</v>
+        <v>3.944460924332971</v>
       </c>
       <c r="M48" s="21" t="inlineStr">
         <is>
@@ -5562,10 +5594,10 @@
         </is>
       </c>
       <c r="N48" s="25" t="n">
-        <v>391450.3267448395</v>
+        <v>406363.2942122668</v>
       </c>
       <c r="O48" s="25" t="n">
-        <v>717658.9323655441</v>
+        <v>744999.3727224916</v>
       </c>
     </row>
     <row r="49"/>
@@ -5620,7 +5652,7 @@
         </is>
       </c>
       <c r="B52" s="32" t="n">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="C52" s="33" t="n">
         <v>1.0039</v>
@@ -5632,7 +5664,7 @@
       </c>
       <c r="E52" s="34" t="inlineStr">
         <is>
-          <t>Paid loss triangle — expect materially longer tail than incurred loss. Selected starting age 203 as least problematic of available options: is_monotone_from_here=False prevents ideal selection, but age 203 shows fewer slope_sign_changes (3 vs 6 at age 143) and lower cv_at_starting_age (0.0108 vs 0.0182). Bondy method selected (simple last observed factor approach) because tail is immaterial at 0.0616% of CDF, qualifying for materiality anchor. No curve fitting required when materiality anchor applies and gap_flag=False. Last observed factor at age 203 stable across early AYs (range 1.0021–1.0327). Alternative scenarios evaluated: double_exp (R²=0.4658, marginal, inf in LOO) rejected due to weak diagnostics; skurnick (tail=1.3291, R²=0.7953) rejected as implausible extreme; modified_bondy variants rejected for exceeding materiality threshold (&gt;0.1% of CDF); mcclenahan essentially unity, less informative than bondy. Monotonicity failure at both starting ages reflects late-age volatility inherent in paid loss development, common at extended durations where incremental claims drive occasional upticks.</t>
+          <t>Paid loss triangle — expect materially longer tail than incurred or count measures. Triangle Type: dollar measure with extended payment patterns. Starting Point Selection: Both ages 143 and 203 evaluated. Age 143 rejected initially due to is_monotone_from_here=False and slope_sign_changes=6, indicating structural instability in observed factors. Age 203 similarly rejected (slope_sign_changes=3). Despite non-monotonic starting points, late-age development is substantively complete based on observed factor levels approaching 1.0. Curve Fit Analysis: All exponential methods (exp_dev_quick, exp_dev_quick_exact_last, exp_dev_product) rejected under Gap Rule — all show gap_flag=True with gap_to_last_observed &gt;0.006, indicating curve does not smoothly connect to observed factors. Poor fit quality (R²=0.204, systematic residual patterns) confirms exponential extrapolation is unreliable. Modified Bondy variants lack diagnostics (R²=N/A) and do not improve materiality profile. McClenahan yields immaterial tail but is designed for count triangles, not dollar measures. Skurnick at age 203 produces tail of 1.329 (R²=0.795, excellent fit quality) but implies ongoing significant development — inconsistent with observed factors at 1.001–1.003 range and creates implausible 3.9% reserve impact. Selected Method: Bondy (last observed factor = 1.0039) selected based on: (1) Materiality anchor applies: tail 0.064% of CDF (&lt;0.1% threshold), rendering materiality_ok=True. (2) Closure anchor: Observed factors at ages 131–143 are all ≤1.024 (av. 1.0175), indicating losses substantively complete. (3) Gap Rule satisfied: gap_flag=False confirms smooth data to cutoff. (4) Simplicity: Given immaterial tail impact, no curve fitting justified. Paid tail (1.0039) &lt; incurred tail would be expected if measured — cross-check deferred to other measures. Prior comparison will validate direction of change.</t>
         </is>
       </c>
       <c r="F52" s="34" t="inlineStr"/>
@@ -5647,16 +5679,16 @@
         <v>143</v>
       </c>
       <c r="C53" s="36" t="n">
-        <v>1.0181</v>
+        <v>1.0472</v>
       </c>
       <c r="D53" s="37" t="inlineStr">
         <is>
-          <t>exp_dev_product</t>
+          <t>exp_dev_quick_exact_last</t>
         </is>
       </c>
       <c r="E53" s="37" t="inlineStr">
         <is>
-          <t>Selected exp_dev_product at age 143 as the balanced choice reflecting mature triangle development. This triangle shows high maturity with observed factors clustering near 1.00-1.05 at age 143+. Bondy (1.0039) is overly conservative for the data profile; exp_dev_quick_exact_last (1.0459) overfits to tail noise via exact last constraint; double_exp at age 203 exhibits numerical instability (inf in LOO max). The exp_dev_product parameterization yields a smooth exponential decay curve with R²=0.23 and LOO std dev=0.0020, acceptable for a mature tail. The 0.28% of CDF is immaterial. Small gap warning (0.008) reflects natural undersmoothing near cutoff in high-maturity data, not a deficiency. This selection respects the triangle's mature development pattern and avoids overfitting to sparse tail cells.</t>
+          <t>Selected exponential decay with exact last observed factor rescaling. This approach balances data-driven rigor with smooth connection to observed development. The triangle shows steady, gradual development through age 143 with 13 contributing accident years. The exponential form better captures the diminishing pace of claims development than conservative Bondy approaches. The exact-last variant explicitly grounds the tail in observed factor at age 131 (last observation before starting age 143), improving actuarial transparency and defensibility. LOO stability (std dev 0.0021) indicates robust parameter estimates. Materiality of 0.74% of CDF is reasonable and appropriately reflects tail uncertainty without being excessive.</t>
         </is>
       </c>
       <c r="F53" s="37" t="inlineStr"/>
@@ -7838,7 +7870,7 @@
       </c>
       <c r="E45" s="34" t="inlineStr">
         <is>
-          <t>Reported count triangle — expect shortest tail of all measures. Selected starting age 143: is_monotone_from_here=True, cv=0.0, slope_sign_changes=0, n_factors_in_fit=12, n_ay_contributing=13. All LDFs from age 143 onward equal 1.0 across all contributing accident years (2001–2013), confirming losses are substantively complete. Bondy method anchors to last observed factor (1.0), which is appropriate when tail is immaterial. No curve fitting needed when closure is definitive. Gap_flag=False confirms smooth transition. Closure anchor strongly applies: all factors at and beyond age 143 are exactly 1.0, indicating 100% development and zero tail risk.</t>
+          <t>Reported Count triangle exhibits shortest tail among all measures. Selected starting age 143: is_monotone_from_here=True, cv=0.0 (zero variance across AYs), slope_sign_changes=0, n_factors_in_fit=12, gap_flag=False. Bondy method appropriate given immaterial tail. Last observed factor at age 143 is 1.0, so all Bondy variants (bondy, modified_bondy_double_dev, modified_bondy_square_ratio) collapse to 1.0. Observed factor pattern demonstrates near-complete reporting by age 95 onward, with all subsequent factors at or extremely close to 1.0 across all accident years. No structural breaks or volatility detected. Alternative starting age 203 valid but fewer data points (7 vs 12 factors). Materiality anchor applies strongly: tail = 1.0 contributes zero additional elongation to CDF, trivially satisfying &lt;0.1% threshold. Closure anchor also applies: reported count development substantially complete by age 143, evidenced by 13 fully-developed accident years (2001-2013) all showing 1.0 at this age, indicating &gt;99% of reported claims are finalized. No curve fitting diagnostics needed when tail is immaterial.</t>
         </is>
       </c>
       <c r="F45" s="34" t="inlineStr"/>
@@ -7850,7 +7882,7 @@
         </is>
       </c>
       <c r="B46" s="35" t="n">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="C46" s="36" t="n">
         <v>1</v>
@@ -7862,7 +7894,7 @@
       </c>
       <c r="E46" s="37" t="inlineStr">
         <is>
-          <t>Reported count triangle exhibits minimal tail development beyond age 35; all observed factors at age 143+ are 1.0. The triangle pattern reflects rapid early reporting (age 23 shows 6–14% development) followed by near-complete stability. Deep tail curve fitting yields no signal (R² and LOO metrics are NaN due to insufficient variability). A tail factor of 1.0 is actuarially sound and reflects observed business reality: reported counts close before age 143. Starting age 203 maximizes available observed data while acknowledging that reported count development is complete in the tail. Bondy method provides smooth mathematical framework, though all scenarios (Bondy, modified Bondy variants) converge to 1.0 tail regardless of method.</t>
+          <t>This count triangle exhibits complete development plateau from age 47 onward, with all observed factors equal to 1.0. The business process shows claims reach final reported count within approximately 4-5 years, with zero subsequent development. Early age volatility (age 23: 1.06-1.14 across recent years) reflects reporting lags and timing variation, but tail development is null. Both Bondy scenarios at ages 143 and 203 converge to 1.0, consistent with the observed data showing no development beyond age 47. The NaN diagnostic values (R², LOO) reflect the statistical absence of variation in the tail, not model failure—this is appropriate for a mature, closed triangle. A tail factor of 1.0 is the only defensible choice given the data exhibits zero tail development.</t>
         </is>
       </c>
       <c r="F46" s="37" t="inlineStr"/>

--- a/sample-data/sample-run/selections/Chain Ladder Selections - Tail.xlsx
+++ b/sample-data/sample-run/selections/Chain Ladder Selections - Tail.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y51"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="L36" s="18" t="n">
-        <v>0.4240093208357876</v>
+        <v>0.397788722563284</v>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="N36" s="19" t="n">
-        <v>1041661.099526353</v>
+        <v>993383.2532688677</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>1909712.015798315</v>
+        <v>1821202.630992919</v>
       </c>
     </row>
     <row r="37">
@@ -2548,20 +2548,20 @@
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
-          <t>[-6.2915378809679625, 0.2512961708153015, -0.008152804041595324]</t>
+          <t>[-6.443260556945541, 0.34069008345644103, -0.01501500915121795]</t>
         </is>
       </c>
       <c r="G37" s="22" t="n">
-        <v>1.174282904895371</v>
+        <v>1.077782958006554</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>0.322764553202301</v>
+        <v>0.3319356148418592</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>0.02925309604738597</v>
+        <v>0.01009648961399146</v>
       </c>
       <c r="J37" s="22" t="n">
-        <v>0.001448090260965058</v>
+        <v>0.0006087900176089292</v>
       </c>
       <c r="K37" s="21" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="L37" s="24" t="n">
-        <v>5.099882875905457</v>
+        <v>2.392276893596306</v>
       </c>
       <c r="M37" s="21" t="inlineStr">
         <is>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="N37" s="25" t="n">
-        <v>897617.484012194</v>
+        <v>932659.4993132614</v>
       </c>
       <c r="O37" s="25" t="n">
-        <v>1645632.054022357</v>
+        <v>1709875.748740982</v>
       </c>
     </row>
     <row r="38">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t>{"r": 0.2438881}</t>
+          <t>{"r": 0.24431098}</t>
         </is>
       </c>
       <c r="G38" s="22" t="n">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="L38" s="24" t="n">
-        <v>2.974769717365426e-13</v>
+        <v>2.865483703161115e-13</v>
       </c>
       <c r="M38" s="21" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="N38" s="25" t="n">
-        <v>1054056.866610702</v>
+        <v>1005204.513982754</v>
       </c>
       <c r="O38" s="25" t="n">
-        <v>1932437.588786285</v>
+        <v>1842874.942301709</v>
       </c>
     </row>
     <row r="39">
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="L39" s="18" t="n">
-        <v>0.8347048613925503</v>
+        <v>0.7832867652919634</v>
       </c>
       <c r="M39" s="15" t="inlineStr">
         <is>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="N39" s="19" t="n">
-        <v>1029553.493466221</v>
+        <v>981836.7981859297</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>1887514.738021411</v>
+        <v>1800034.130007543</v>
       </c>
     </row>
     <row r="40">
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="L40" s="18" t="n">
-        <v>0.8395145101459963</v>
+        <v>0.787802491804133</v>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="N40" s="19" t="n">
-        <v>1029411.107348897</v>
+        <v>981701.0112351663</v>
       </c>
       <c r="O40" s="19" t="n">
-        <v>1887253.696806315</v>
+        <v>1799785.187264461</v>
       </c>
     </row>
     <row r="41">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="L41" s="18" t="n">
-        <v>0.4240093208357876</v>
+        <v>0.397788722563284</v>
       </c>
       <c r="M41" s="15" t="inlineStr">
         <is>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="N41" s="19" t="n">
-        <v>1041661.099526353</v>
+        <v>993383.2532688677</v>
       </c>
       <c r="O41" s="19" t="n">
-        <v>1909712.015798315</v>
+        <v>1821202.630992919</v>
       </c>
     </row>
     <row r="42">
@@ -2797,20 +2797,20 @@
       </c>
       <c r="F42" s="21" t="inlineStr">
         <is>
-          <t>[-6.185922875367714, 0.6521830536724201, -0.05780619764194905]</t>
+          <t>[-6.198815549455116, 0.8016226533428397, -0.08285309337556246]</t>
         </is>
       </c>
       <c r="G42" s="22" t="n">
-        <v>1.036724577767118</v>
+        <v>1.021551350628563</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>0.7285744780786501</v>
+        <v>0.8862026012818859</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>0.01078619293771597</v>
+        <v>0.003719995419637236</v>
       </c>
       <c r="J42" s="22" t="n">
-        <v>5.820121268061695e-05</v>
+        <v>3.183582064846544e-05</v>
       </c>
       <c r="K42" s="21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="L42" s="24" t="n">
-        <v>1.266396803066497</v>
+        <v>0.711357612757944</v>
       </c>
       <c r="M42" s="21" t="inlineStr">
         <is>
@@ -2826,57 +2826,61 @@
         </is>
       </c>
       <c r="N42" s="25" t="n">
-        <v>1016718.315756459</v>
+        <v>983998.0274748318</v>
       </c>
       <c r="O42" s="25" t="n">
-        <v>1863983.578886852</v>
+        <v>1803996.383703869</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="n">
+      <c r="A43" s="20" t="n">
         <v>203</v>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C43" s="16" t="n">
+      <c r="C43" s="22" t="n">
         <v>0.01123156187314335</v>
       </c>
-      <c r="D43" s="17" t="n">
+      <c r="D43" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>modified_bondy_double_dev</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="inlineStr"/>
-      <c r="G43" s="16" t="n">
-        <v>1.0238</v>
-      </c>
-      <c r="H43" s="16" t="n"/>
-      <c r="I43" s="16" t="n"/>
-      <c r="J43" s="16" t="n"/>
-      <c r="K43" s="15" t="inlineStr">
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t>mcclenahan</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t>{"r": 0.26072697}</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="n">
+        <v>1.000000000000038</v>
+      </c>
+      <c r="H43" s="22" t="n"/>
+      <c r="I43" s="22" t="n"/>
+      <c r="J43" s="22" t="n"/>
+      <c r="K43" s="21" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L43" s="18" t="n">
-        <v>0.8347048613925503</v>
-      </c>
-      <c r="M43" s="15" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N43" s="19" t="n">
-        <v>1029553.493466221</v>
-      </c>
-      <c r="O43" s="19" t="n">
-        <v>1887514.738021411</v>
+      <c r="L43" s="24" t="n">
+        <v>1.289467666422451e-12</v>
+      </c>
+      <c r="M43" s="21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N43" s="25" t="n">
+        <v>1005204.513982724</v>
+      </c>
+      <c r="O43" s="25" t="n">
+        <v>1842874.94230165</v>
       </c>
     </row>
     <row r="44">
@@ -2896,12 +2900,12 @@
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>modified_bondy_square_ratio</t>
+          <t>modified_bondy_double_dev</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr"/>
       <c r="G44" s="16" t="n">
-        <v>1.02394161</v>
+        <v>1.0238</v>
       </c>
       <c r="H44" s="16" t="n"/>
       <c r="I44" s="16" t="n"/>
@@ -2912,7 +2916,7 @@
         </is>
       </c>
       <c r="L44" s="18" t="n">
-        <v>0.8395145101459963</v>
+        <v>0.7832867652919634</v>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
@@ -2920,122 +2924,169 @@
         </is>
       </c>
       <c r="N44" s="19" t="n">
-        <v>1029411.107348897</v>
+        <v>981836.7981859297</v>
       </c>
       <c r="O44" s="19" t="n">
-        <v>1887253.696806315</v>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+        <v>1800034.130007543</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="n">
+        <v>203</v>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="n">
+        <v>0.01123156187314335</v>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>modified_bondy_square_ratio</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr"/>
+      <c r="G45" s="16" t="n">
+        <v>1.02394161</v>
+      </c>
+      <c r="H45" s="16" t="n"/>
+      <c r="I45" s="16" t="n"/>
+      <c r="J45" s="16" t="n"/>
+      <c r="K45" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L45" s="18" t="n">
+        <v>0.787802491804133</v>
+      </c>
+      <c r="M45" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N45" s="19" t="n">
+        <v>981701.0112351663</v>
+      </c>
+      <c r="O45" s="19" t="n">
+        <v>1799785.187264461</v>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>Tail Factor Selection</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="3" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>Cutoff Age</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>Tail Factor</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F48" s="9" t="inlineStr">
         <is>
           <t>Additional Notes</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="26" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="26" t="inlineStr">
         <is>
           <t>Rules-Based AI Selection</t>
         </is>
       </c>
-      <c r="B48" s="32" t="n">
+      <c r="B49" s="32" t="n">
         <v>203</v>
       </c>
-      <c r="C48" s="33" t="n">
-        <v>1.036724577767118</v>
-      </c>
-      <c r="D48" s="34" t="inlineStr">
+      <c r="C49" s="33" t="n">
+        <v>1.021551350628563</v>
+      </c>
+      <c r="D49" s="34" t="inlineStr">
         <is>
           <t>double_exp</t>
         </is>
       </c>
-      <c r="E48" s="34" t="inlineStr">
-        <is>
-          <t>Incurred Loss triangle—medium tail expected, longer than Reported Count, shorter than Paid Loss. Starting point criteria fail at both ages due to volatility (is_monotone_from_here=False, slope_sign_changes &gt; 0 at both 143 and 203). This is typical for incurred triangles with medical reserves and reopened claims. Double exponential curve selected at age 203 as best available option. Curve fit diagnostics: r_squared=0.7286 (below ideal 0.85 but acceptable for tail-only region), loo_std_dev=0.0108 (moderate AY sensitivity, acceptable), gap_to_last_observed=0.000058 (excellent), gap_flag=False (PASSES hard Gap Rule). Tail factor 1.0367 represents ~1.3% of CDF (materiality_ok=False, but material tail is appropriate for incurred). Reserve impact moderate (~1.0M range). Residuals show no systematic sign pattern; curve fit is stable. Age 143 double_exp rejected (poor R²=0.323, higher pct_of_cdf=5.1%). Age 143 Bondy rejected as too simplistic (ignores decay pattern). Age 203 double_exp provides theoretically sound exponential decay with strong gap and residual diagnostics, best balance for volatile incurred data. ASOP 43 compliant.</t>
-        </is>
-      </c>
-      <c r="F48" s="34" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="28" t="inlineStr">
+      <c r="E49" s="34" t="inlineStr">
+        <is>
+          <t>Incurred Loss triangle expects medium tail, materially longer than Reported Count but shorter than Paid Loss. Starting age 203 selected: monotonicity check fails (slope_sign_changes=5) but improves significantly from age 143 (9 sign changes), CV=0.0112 (excellent), n_factors=7 meeting minimum. Double exponential provides superior fit diagnostics: R²=0.8862 (well above 0.85 threshold), LOO std dev=0.0037 (stable), gap to last observed=3.2e-05 (immaterial, gap_flag=False). Tail materiality ~0.71% of CDF warrants careful method selection; double_exp balances good fit quality with economical tail estimate. Residual analysis shows sparse anomalies without systematic bias. Bondy (tail=1.0119) rejected due to materiality &gt;0.1%; Bondy and modified variants immaterial rationale not applicable. McClenahan trivial tail (1.0) undershoots observed development. Alternative methods (exp_dev_quick R²=0.32, mcclenahan tail=1.0) lack fit quality or economic substance. Selection reflects ASOP 43 requirement for documented method choice and fit validation.</t>
+        </is>
+      </c>
+      <c r="F49" s="34" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="28" t="inlineStr">
         <is>
           <t>Open-Ended AI Selection</t>
         </is>
       </c>
-      <c r="B49" s="35" t="n">
+      <c r="B50" s="35" t="n">
         <v>203</v>
       </c>
-      <c r="C49" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="37" t="inlineStr">
-        <is>
-          <t>mcclenahan</t>
-        </is>
-      </c>
-      <c r="E49" s="37" t="inlineStr">
-        <is>
-          <t>Incurred loss triangle exhibits rapid development closure by age 143, with observed factors clustering near 1.0 thereafter. McClenahan (r=0.2439 at age 143, r=0.5388 at age 203) correctly identifies essential tail closure across both starting points. All scenarios at ages 143 and 203 produce factors at or near 1.0, with Bondy/modified variants yielding only 1.01–1.024. Double Exponential at age 143 (R²=0.323) shows poor fit quality. At age 203, double exponential improves (R²=0.729) but still produces only 1.0367. The observed data shows no meaningful tail development beyond age 143—later factors are predominantly 1.0. McClenahan's null tail correctly reflects the actuarial reality that this workers comp book is substantially developed by the selected starting age. Selection anchors to demonstrated closure in the triangle itself.</t>
-        </is>
-      </c>
-      <c r="F49" s="37" t="inlineStr"/>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="30" t="inlineStr">
+      <c r="C50" s="36" t="n">
+        <v>1.0216</v>
+      </c>
+      <c r="D50" s="37" t="inlineStr">
+        <is>
+          <t>double_exp</t>
+        </is>
+      </c>
+      <c r="E50" s="37" t="inlineStr">
+        <is>
+          <t>Incurred loss exhibits more tail development volatility than paid loss, with observed factors showing modest but non-negligible development beyond age 143. The Double Exponential method at age 203 delivers a tail factor of 1.0216 supported by strong diagnostics: R² = 0.886 (excellent fit to sparse tail), tight LOO stability (std_dev = 0.0037), and minimal gap to last observed (0.000032). Age 203 better captures the lingering development than age 143, where R² drops to 0.332. McClenahan's near-unity estimate at both ages inadequately reflects the observed development intensity. The 1.0216 factor is material (0.71% of CDF) and justified by incurred's characteristic longer tail relative to paid. This selection balances observed development, diagnostic strength, and actuarial reasonableness.</t>
+        </is>
+      </c>
+      <c r="F50" s="37" t="inlineStr"/>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="30" t="inlineStr">
         <is>
           <t>User Selection</t>
         </is>
       </c>
-      <c r="B51" s="31" t="inlineStr"/>
-      <c r="C51" s="31" t="inlineStr"/>
-      <c r="D51" s="31" t="inlineStr"/>
-      <c r="E51" s="31" t="inlineStr"/>
-      <c r="F51" s="31" t="inlineStr"/>
+      <c r="B52" s="31" t="inlineStr"/>
+      <c r="C52" s="31" t="inlineStr"/>
+      <c r="D52" s="31" t="inlineStr"/>
+      <c r="E52" s="31" t="inlineStr"/>
+      <c r="F52" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A5:Y5"/>
     <mergeCell ref="A34:O34"/>
@@ -4919,7 +4970,7 @@
         </is>
       </c>
       <c r="L36" s="18" t="n">
-        <v>0.06228392439428904</v>
+        <v>0.05767680903064931</v>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
@@ -4927,10 +4978,10 @@
         </is>
       </c>
       <c r="N36" s="19" t="n">
-        <v>522894.7693890631</v>
+        <v>489199.6169315651</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>958640.4105466083</v>
+        <v>896865.9643745348</v>
       </c>
     </row>
     <row r="37">
@@ -4955,28 +5006,28 @@
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
-          <t>[0.011941365596704483, 0.8717942642959445]</t>
+          <t>[0.016571709809195413, 0.8431024219307085]</t>
         </is>
       </c>
       <c r="G37" s="22" t="n">
-        <v>1.018095619722987</v>
+        <v>1.013703181942844</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>0.2308473328047094</v>
+        <v>0.3537649435694358</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>0.002004170803278808</v>
+        <v>0.001678601511099865</v>
       </c>
       <c r="J37" s="22" t="n">
-        <v>0.008158634403295523</v>
+        <v>0.0009282901908046585</v>
       </c>
       <c r="K37" s="21" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L37" s="24" t="n">
-        <v>0.2843287039380108</v>
+        <v>0.2004089016851266</v>
       </c>
       <c r="M37" s="21" t="inlineStr">
         <is>
@@ -4984,10 +5035,10 @@
         </is>
       </c>
       <c r="N37" s="25" t="n">
-        <v>515603.8871206492</v>
+        <v>484468.7322539017</v>
       </c>
       <c r="O37" s="25" t="n">
-        <v>945273.7930545285</v>
+        <v>888192.6757988185</v>
       </c>
     </row>
     <row r="38">
@@ -5012,28 +5063,28 @@
       </c>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t>[0.011941365596704483, 0.8717942642959445]</t>
+          <t>[0.016571709809195413, 0.8431024219307085]</t>
         </is>
       </c>
       <c r="G38" s="22" t="n">
-        <v>1.031078396186502</v>
+        <v>1.026964587131287</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>0.2308473328047094</v>
+        <v>0.3537649435694358</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>0.002004170803278808</v>
+        <v>0.001678601511099865</v>
       </c>
       <c r="J38" s="22" t="n">
-        <v>0.008158634403295523</v>
+        <v>0.0009282901908046585</v>
       </c>
       <c r="K38" s="21" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L38" s="24" t="n">
-        <v>0.4812207520450426</v>
+        <v>0.3885306502651198</v>
       </c>
       <c r="M38" s="21" t="inlineStr">
         <is>
@@ -5041,10 +5092,10 @@
         </is>
       </c>
       <c r="N38" s="25" t="n">
-        <v>509111.6843599677</v>
+        <v>478212.6877514347</v>
       </c>
       <c r="O38" s="25" t="n">
-        <v>933371.4213266</v>
+        <v>876723.2608776242</v>
       </c>
     </row>
     <row r="39">
@@ -5069,28 +5120,28 @@
       </c>
       <c r="F39" s="21" t="inlineStr">
         <is>
-          <t>[0.011941365596704483, 0.8717942642959445]</t>
+          <t>[0.016571709809195413, 0.8431024219307085]</t>
         </is>
       </c>
       <c r="G39" s="22" t="n">
-        <v>1.045910828459935</v>
+        <v>1.041477001913356</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>0.2308473328047094</v>
+        <v>0.3537649435694358</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>0.002004170803278808</v>
+        <v>0.001678601511099865</v>
       </c>
       <c r="J39" s="22" t="n">
-        <v>0.008158634403295523</v>
+        <v>0.0009282901908046585</v>
       </c>
       <c r="K39" s="21" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L39" s="24" t="n">
-        <v>0.699270656982969</v>
+        <v>0.5881302887140961</v>
       </c>
       <c r="M39" s="21" t="inlineStr">
         <is>
@@ -5098,10 +5149,10 @@
         </is>
       </c>
       <c r="N39" s="25" t="n">
-        <v>501891.7910646573</v>
+        <v>471549.0544057712</v>
       </c>
       <c r="O39" s="25" t="n">
-        <v>920134.9502852112</v>
+        <v>864506.5997439101</v>
       </c>
     </row>
     <row r="40">
@@ -5126,11 +5177,11 @@
       </c>
       <c r="F40" s="21" t="inlineStr">
         <is>
-          <t>{"r": 0.40152706}</t>
+          <t>{"r": 0.55556888}</t>
         </is>
       </c>
       <c r="G40" s="22" t="n">
-        <v>1.000000000765223</v>
+        <v>1.0000013320688</v>
       </c>
       <c r="H40" s="22" t="n"/>
       <c r="I40" s="22" t="n"/>
@@ -5141,7 +5192,7 @@
         </is>
       </c>
       <c r="L40" s="24" t="n">
-        <v>1.227609617860993e-08</v>
+        <v>1.978807845252076e-05</v>
       </c>
       <c r="M40" s="21" t="inlineStr">
         <is>
@@ -5149,10 +5200,10 @@
         </is>
       </c>
       <c r="N40" s="25" t="n">
-        <v>524934.0585879907</v>
+        <v>491106.8412494883</v>
       </c>
       <c r="O40" s="25" t="n">
-        <v>962379.1074113175</v>
+        <v>900362.5422907323</v>
       </c>
     </row>
     <row r="41">
@@ -5188,7 +5239,7 @@
         </is>
       </c>
       <c r="L41" s="18" t="n">
-        <v>0.1240091542280136</v>
+        <v>0.114841496587679</v>
       </c>
       <c r="M41" s="15" t="inlineStr">
         <is>
@@ -5196,10 +5247,10 @@
         </is>
       </c>
       <c r="N41" s="19" t="n">
-        <v>520871.2631372064</v>
+        <v>487306.5047009289</v>
       </c>
       <c r="O41" s="19" t="n">
-        <v>954930.6490848809</v>
+        <v>893395.2586183697</v>
       </c>
     </row>
     <row r="42">
@@ -5235,7 +5286,7 @@
         </is>
       </c>
       <c r="L42" s="18" t="n">
-        <v>0.1242487987507122</v>
+        <v>0.1150634452564325</v>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
@@ -5243,10 +5294,10 @@
         </is>
       </c>
       <c r="N42" s="19" t="n">
-        <v>520863.4021207914</v>
+        <v>487299.1502456069</v>
       </c>
       <c r="O42" s="19" t="n">
-        <v>954916.2372214496</v>
+        <v>893381.7754502818</v>
       </c>
     </row>
     <row r="43">
@@ -5282,7 +5333,7 @@
         </is>
       </c>
       <c r="L43" s="18" t="n">
-        <v>0.06228392439428904</v>
+        <v>0.05767680903064931</v>
       </c>
       <c r="M43" s="15" t="inlineStr">
         <is>
@@ -5290,10 +5341,10 @@
         </is>
       </c>
       <c r="N43" s="19" t="n">
-        <v>522894.7693890631</v>
+        <v>489199.6169315651</v>
       </c>
       <c r="O43" s="19" t="n">
-        <v>958640.4105466083</v>
+        <v>896865.9643745348</v>
       </c>
     </row>
     <row r="44">
@@ -5318,18 +5369,20 @@
       </c>
       <c r="F44" s="21" t="inlineStr">
         <is>
-          <t>[-6.0197845785918815, 0.24717142993689123, -0.016926013800853207]</t>
+          <t>[-6.09612748068809, 0.3838096387678443, -0.03959570862874873]</t>
         </is>
       </c>
       <c r="G44" s="22" t="n">
-        <v>1.045603069011225</v>
+        <v>1.016282359093023</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>0.4657683173472149</v>
-      </c>
-      <c r="I44" s="22" t="n"/>
+        <v>0.5340751389078572</v>
+      </c>
+      <c r="I44" s="22" t="n">
+        <v>0.04647288677542463</v>
+      </c>
       <c r="J44" s="22" t="n">
-        <v>0.0001301930542501879</v>
+        <v>0.0001515701072505433</v>
       </c>
       <c r="K44" s="21" t="inlineStr">
         <is>
@@ -5337,7 +5390,7 @@
         </is>
       </c>
       <c r="L44" s="24" t="n">
-        <v>0.6948187443854217</v>
+        <v>0.2374368772121291</v>
       </c>
       <c r="M44" s="21" t="inlineStr">
         <is>
@@ -5345,10 +5398,10 @@
         </is>
       </c>
       <c r="N44" s="25" t="n">
-        <v>502039.5162822977</v>
+        <v>483239.2209148258</v>
       </c>
       <c r="O44" s="25" t="n">
-        <v>920405.7798508778</v>
+        <v>885938.5716771781</v>
       </c>
     </row>
     <row r="45">
@@ -5373,11 +5426,11 @@
       </c>
       <c r="F45" s="21" t="inlineStr">
         <is>
-          <t>{"r": 0.53879871}</t>
+          <t>{"r": 0.53267096}</t>
         </is>
       </c>
       <c r="G45" s="22" t="n">
-        <v>1.000000658371182</v>
+        <v>1.000000506133965</v>
       </c>
       <c r="H45" s="22" t="n"/>
       <c r="I45" s="22" t="n"/>
@@ -5388,7 +5441,7 @@
         </is>
       </c>
       <c r="L45" s="24" t="n">
-        <v>1.056192008174933e-05</v>
+        <v>7.51870181748353e-06</v>
       </c>
       <c r="M45" s="21" t="inlineStr">
         <is>
@@ -5396,10 +5449,10 @@
         </is>
       </c>
       <c r="N45" s="25" t="n">
-        <v>524933.7133884504</v>
+        <v>491107.246871531</v>
       </c>
       <c r="O45" s="25" t="n">
-        <v>962378.4745454863</v>
+        <v>900363.2859311476</v>
       </c>
     </row>
     <row r="46">
@@ -5435,7 +5488,7 @@
         </is>
       </c>
       <c r="L46" s="18" t="n">
-        <v>0.1240091542280136</v>
+        <v>0.114841496587679</v>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
@@ -5443,10 +5496,10 @@
         </is>
       </c>
       <c r="N46" s="19" t="n">
-        <v>520871.2631372064</v>
+        <v>487306.5047009289</v>
       </c>
       <c r="O46" s="19" t="n">
-        <v>954930.6490848809</v>
+        <v>893395.2586183697</v>
       </c>
     </row>
     <row r="47">
@@ -5482,7 +5535,7 @@
         </is>
       </c>
       <c r="L47" s="18" t="n">
-        <v>0.1242487987507122</v>
+        <v>0.1150634452564325</v>
       </c>
       <c r="M47" s="15" t="inlineStr">
         <is>
@@ -5490,10 +5543,10 @@
         </is>
       </c>
       <c r="N47" s="19" t="n">
-        <v>520863.4021207914</v>
+        <v>487299.1502456069</v>
       </c>
       <c r="O47" s="19" t="n">
-        <v>954916.2372214496</v>
+        <v>893381.7754502818</v>
       </c>
     </row>
     <row r="48">
@@ -5535,7 +5588,7 @@
         </is>
       </c>
       <c r="L48" s="24" t="n">
-        <v>3.820774154146964</v>
+        <v>3.548023263185676</v>
       </c>
       <c r="M48" s="21" t="inlineStr">
         <is>
@@ -5543,10 +5596,10 @@
         </is>
       </c>
       <c r="N48" s="25" t="n">
-        <v>394946.3031407148</v>
+        <v>369496.1042175144</v>
       </c>
       <c r="O48" s="25" t="n">
-        <v>724068.2224246487</v>
+        <v>677409.5243987739</v>
       </c>
     </row>
     <row r="49"/>
@@ -5601,7 +5654,7 @@
         </is>
       </c>
       <c r="B52" s="32" t="n">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="C52" s="33" t="n">
         <v>1.0039</v>
@@ -5613,7 +5666,7 @@
       </c>
       <c r="E52" s="34" t="inlineStr">
         <is>
-          <t>Paid Loss triangle—longest tail expected among measures. Both starting ages fail monotonicity criteria (is_monotone_from_here=False, slope_sign_changes 6 and 3 at ages 143 and 203 respectively); structural breaks in paid cash flows are typical for long-tail workers compensation. Age 143 exponential methods (exp_dev_quick, exp_dev_quick_exact_last, exp_dev_product) all fail hard Gap Rule (gap_flag=True)—REJECTED. Age 203 double_exp passes Gap Rule (gap_flag=False) but produces material tail (pct_of_cdf=0.695%, r_squared=0.4658). Bondy (1.0039) selected at age 143: passes Gap Rule (gap_flag=False), immaterial tail (pct_of_cdf=0.062%, materiality_ok=True), stable by construction (no fit required), carries forward observed last factor. Materiality anchor applies strongly—tail is negligible. Reserve impact moderate (~600k range, comparable to double_exp alternatives). Bondy prioritizes simplicity and materiality for dollar measure with late-age volatility. While double_exp offers richer theoretical framework, Bondy's materiality anchor is superior and supports ASOP 43 principle of using simplest adequate method. This selection is most defensible for a dollar measure with structural breaks. ASOP 43 compliant.</t>
+          <t>Paid Loss triangle expects longest tail among dollar measures; however, diagnostics reveal materially immaterial tail development. Starting age 203 selected over age 143: slope_sign_changes reduce from 6 to 3, CV=0.0108 (low), n_factors=7 meeting minimum. Bondy method selected based on materiality anchor: pct_of_cdf=0.058% is well below 0.1% immateriality threshold, indicating tail contributes negligibly to CDF. Gap to last observed factor minimal (gap_flag=False). Curve fits (exp_dev_quick R²=0.354, double_exp LOO std dev=0.0465) lack quality diagnostics and are rejected: exp_dev_quick fails R²&gt;0.85 requirement; double_exp shows unstable LOO performance. McClenahan and modified Bondy variants also rejected—neither improves on immateriality anchor or fit. Skurnick extreme outlier (tail=1.329) inconsistent with observed monotonic decay and rejected. Bondy method (last observed factor=1.0039 at age 203) is appropriate default when immateriality applies, following hierarchy that prioritizes materiality over complex curve fits. Selection ASOP 43 compliant: documented method choice with materiality justification; no curve fit required where tail immaterial.</t>
         </is>
       </c>
       <c r="F52" s="34" t="inlineStr"/>
@@ -5625,7 +5678,7 @@
         </is>
       </c>
       <c r="B53" s="35" t="n">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="C53" s="36" t="n">
         <v>1.0039</v>
@@ -5637,7 +5690,7 @@
       </c>
       <c r="E53" s="37" t="inlineStr">
         <is>
-          <t>Paid loss exhibits clean, rapid tail closure. At age 143: Bondy yields 1.0039 (materiality_ok=True, immaterial 0.062% of CDF); McClenahan produces 1.0000; exp_dev_quick_exact_last = 1.0459 with weak R²=0.231 and gap_flag=True. At age 203: Bondy again = 1.0039 (materiality_ok=True); double exponential = 1.0456 with improved R²=0.467 but loo_max=inf signals potential instability; McClenahan ≈ 1.0. CV at age 143 is only 0.018, indicating minimal remaining development. Observed factors show rapid decay—early ages drive the reserve build, tail factors are nearly flat. Bondy at age 203 is preferred: immaterial tail, consistent across both starting points, materiality_ok flag confirms defensibility, and avoids the fitting artifacts of exponential variants. Slight positive tail of 0.39% reasonably captures any minor tail uncertainty while remaining actuarially conservative.</t>
+          <t>At age 143, paid development is essentially complete with observed factors tightly clustered near 1.0 from age 143–287. The Bondy method yields 1.0039 with materiality_ok=True and passes the basic monotonicity check given the sparse tail. The gap to last observed (0.0009) is immaterial. While exponential decay methods fit the late-age data with modest R² (0.354), they produce inflated tail factors (1.027–1.041) that exceed the natural pattern of near-unity development in the tail. Bondy is the most defensible conservative choice, anchored in the observed tight factors and materiality constraints. No material justification exists for a larger tail beyond 1.0039.</t>
         </is>
       </c>
       <c r="F53" s="37" t="inlineStr"/>
@@ -7819,7 +7872,7 @@
       </c>
       <c r="E45" s="34" t="inlineStr">
         <is>
-          <t>Reported Count triangle—shortest tail expected. Bondy tail factor 1.0 selected at starting age 143. Criteria satisfied: is_monotone_from_here=True, cv=0.0, slope_sign_changes=0, n_factors_in_fit=12. Observed factor at age 143 is 1.0; Bondy carries forward this last finite factor. All reported count factors remain at 1.0 from age 143 onward—early closure evident in data. Gap_flag=False; no disconnection. Materiality anchor applies: pct_of_cdf is negligible (tail immaterial, &lt;0.1%). Closure anchor applies: all reported claims exhausted by mid-development. Reserve impact negligible; count triangle has fully closed by this age. This is the appropriate selection for a count measure with rapid closure. ASOP 43 compliant.</t>
+          <t>Reported Count triangle exhibits shortest tail of all measures — factors are 1.0 from age 143 onward (zero development). Starting age 143 satisfies monotonicity (is_monotone_from_here=True), zero CV, zero slope sign changes, and 12 factors in fit. No curve fit diagnostics required. Tail immateriality anchor applies: pct_of_cdf not evaluated due to zero development (tail immaterial). Bondy method (last observed factor = 1.0) is appropriate default for reported count where development has ceased. Gap to last observed negligible (gap_flag=False). ASOP 43 compliant: tail selection reflects completed reporting pattern; no future development expected in reported counts.</t>
         </is>
       </c>
       <c r="F45" s="34" t="inlineStr"/>
@@ -7843,7 +7896,7 @@
       </c>
       <c r="E46" s="37" t="inlineStr">
         <is>
-          <t>Reported count triangle is fully developed by age 143. All scenarios (Bondy, modified_bondy variants) at both starting ages (143 and 203) produce tail_factor = 1.0 with is_monotone = True and cv = 0.0. Observed factors show the count development closes by age ~95, with all subsequent ages equal to 1.0. No curve fitting method produces meaningful tail development—the uniform 1.0 across all methods reflects complete closure of the count triangle. This is typical for workers comp claim counts, which materialize rapidly relative to claim amounts. Selection at age 143 captures the point of development completion, and the null tail factor of 1.0 is the only defensible choice. No further development should be projected beyond the observed data.</t>
+          <t>Reported count is a closed triangle with development to unity occurring by the earliest reporting age (23). All observed factors from age 35 onward are at or effectively at 1.0, with only minor noise at early ages. All fitting methods yield tail_factor = 1.0, cv_at_starting_age = 0.0, and is_monotone_from_here = True, confirming complete maturity. Materiality is marked N/A, reflecting the irrelevance of tail selection for this measure. Any tail factor other than 1.0 would be indefensible. Bondy at age 143 is selected by convention; all methods agree on the trivial tail.</t>
         </is>
       </c>
       <c r="F46" s="37" t="inlineStr"/>
